--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_1.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_1.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9C1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9C2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10C1" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10C2" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11C1" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11C2" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12C1" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12C2" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="9C1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="9C2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="10C1" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="10C2" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="11C1" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="11C2" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="12C1" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="12C2" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'9C1'!$A$2:$D$22</definedName>
@@ -527,17 +527,17 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 17/08/2026 — 1º e 2º tempos</t>
+          <t>Terça, 18/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
@@ -547,17 +547,17 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Terça, 18/08/2026 — 3º e 4º tempos</t>
+          <t>Sexta, 21/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -567,17 +567,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 19/08/2026 — 1º e 2º tempos</t>
+          <t>Quarta, 26/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -587,17 +587,17 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 24/08/2026 — 5º e 6º tempos</t>
+          <t>Quinta, 27/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -607,17 +607,17 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Terça, 25/08/2026 — 5º e 6º tempos</t>
+          <t>Quarta, 02/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -627,17 +627,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Terça, 01/09/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 03/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -647,17 +647,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 09/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -667,17 +667,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 10/09/2026 — 5º e 6º tempos</t>
+          <t>Sexta, 11/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -687,17 +687,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Terça, 15/09/2026 — 3º e 4º tempos</t>
+          <t>Quarta, 16/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -707,81 +707,81 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 21/09/2026 — 5º e 6º tempos</t>
+          <t>Quarta, 23/09/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>AG9</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 02/10/2026 — 2º ao 7º tempos</t>
+          <t>Quinta, 24/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>AG9</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 05/10/2026 — 1º e 2º tempos</t>
+          <t>Sexta, 02/10/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 19/10/2026 — 1º tempo</t>
+          <t>Terça, 06/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -797,7 +797,7 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -807,17 +807,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 26/10/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 23/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -827,17 +827,17 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 30/10/2026 — 7º tempo</t>
+          <t>Segunda, 26/10/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -847,17 +847,17 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 05/11/2026 — 5º e 6º tempos</t>
+          <t>Sexta, 06/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -867,17 +867,17 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Terça, 10/11/2026 — 1º e 2º tempos</t>
+          <t>Quarta, 11/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -887,17 +887,17 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 12/11/2026 — 7º tempo</t>
+          <t>Segunda, 16/11/2026 — 1º tempo</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -907,17 +907,17 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Terça, 17/11/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 19/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -990,7 +990,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 17/08/2026 — 6º e 7º tempos</t>
+          <t>Terça, 18/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
@@ -1000,17 +1000,17 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Terça, 18/08/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 21/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -1020,17 +1020,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 24/08/2026 — 3º e 4º tempos</t>
+          <t>Quarta, 26/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -1040,17 +1040,17 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 28/08/2026 — 5º e 6º tempos</t>
+          <t>Quinta, 27/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -1060,17 +1060,17 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 31/08/2026 — 5º e 6º tempos</t>
+          <t>Quarta, 02/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -1080,17 +1080,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 02/09/2026 — 3º e 4º tempos</t>
+          <t>Quinta, 03/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -1100,17 +1100,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 1º e 2º tempos</t>
+          <t>Quarta, 09/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -1120,17 +1120,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 10/09/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 11/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -1140,17 +1140,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 14/09/2026 — 3º e 4º tempos</t>
+          <t>Quarta, 16/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -1160,37 +1160,37 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 23/09/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 21/09/2026 — 5º e 6º tempos</t>
+          <t>Quinta, 24/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
@@ -1200,57 +1200,57 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>AG9</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Terça, 22/09/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 02/10/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>AG9</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 02/10/2026 — 2º ao 7º tempos</t>
+          <t>Terça, 06/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 05/10/2026 — 6º e 7º tempos</t>
+          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -1260,17 +1260,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 23/10/2026 — 5º e 6º tempos</t>
+          <t>Sexta, 23/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -1280,77 +1280,77 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 3º e 4º tempos</t>
+          <t>Segunda, 26/10/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Terça, 03/11/2026 — 1º tempo</t>
+          <t>Sexta, 06/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 11/11/2026 — 2º tempo</t>
+          <t>Quarta, 11/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 16/11/2026 — 2º tempo</t>
+          <t>Segunda, 16/11/2026 — 1º tempo</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -1360,17 +1360,17 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Terça, 17/11/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 19/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -1433,12 +1433,12 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -1453,17 +1453,17 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Terça, 18/08/2026 — 6º e 7º tempos</t>
+          <t>Quarta, 19/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -1473,37 +1473,37 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 19/08/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 20/08/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 24/08/2026 — 3º e 4º tempos</t>
+          <t>Segunda, 24/08/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -1513,17 +1513,17 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Terça, 25/08/2026 — 5º e 6º tempos</t>
+          <t>Terça, 25/08/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -1533,37 +1533,37 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 28/08/2026 — 2º ao 4º tempos</t>
+          <t>Segunda, 31/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 31/08/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 03/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -1573,17 +1573,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 5º e 6º tempos</t>
+          <t>Sexta, 04/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -1613,17 +1613,17 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 10/09/2026 — 3º e 4º tempos</t>
+          <t>Quinta, 10/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -1653,17 +1653,17 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 14/09/2026 — 3º e 4º tempos</t>
+          <t>Segunda, 14/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -1673,77 +1673,77 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 21/09/2026 — 1º ao 3º tempos</t>
+          <t>Quarta, 16/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 23/09/2026 — 1º tempo</t>
+          <t>Quarta, 23/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 01/10/2026 — 5º e 6º tempos</t>
+          <t>Sexta, 25/09/2026 — 5º tempo</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 05/10/2026 — 1º e 2º tempos</t>
+          <t>Segunda, 28/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -1753,17 +1753,17 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Terça, 06/10/2026 — 6º e 7º tempos</t>
+          <t>Sexta, 02/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -1773,17 +1773,17 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 19/10/2026 — 1º e 2º tempos</t>
+          <t>Terça, 06/10/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -1793,57 +1793,57 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 26/10/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 19/10/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 5º tempo</t>
+          <t>Segunda, 26/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Terça, 03/11/2026 — 5º e 6º tempos</t>
+          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -1853,37 +1853,37 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 11/11/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 04/11/2026 — 1º tempo</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 12/11/2026 — 3º e 4º tempos</t>
+          <t>Quinta, 12/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 17/08/2026 — 3º e 4º tempos</t>
+          <t>Segunda, 17/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
@@ -1966,17 +1966,17 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Terça, 18/08/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 19/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -1986,37 +1986,37 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 19/08/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 20/08/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 24/08/2026 — 6º e 7º tempos</t>
+          <t>Segunda, 24/08/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -2026,37 +2026,37 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 27/08/2026 — 1º ao 3º tempos</t>
+          <t>Terça, 25/08/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 31/08/2026 — 5º e 6º tempos</t>
+          <t>Terça, 01/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -2066,17 +2066,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Terça, 01/09/2026 — 5º e 6º tempos</t>
+          <t>Quinta, 03/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 02/09/2026 — 1º e 2º tempos</t>
+          <t>Sexta, 04/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 1º e 2º tempos</t>
+          <t>Quarta, 09/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -2126,17 +2126,17 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 10/09/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 10/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -2166,57 +2166,57 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 14/09/2026 — 1º ao 3º tempos</t>
+          <t>Segunda, 14/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 18/09/2026 — 5º tempo</t>
+          <t>Quarta, 16/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 21/09/2026 — 6º e 7º tempos</t>
+          <t>Quarta, 23/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -2226,37 +2226,37 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 28/09/2026 — 3º e 4º tempos</t>
+          <t>Sexta, 25/09/2026 — 5º tempo</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Terça, 06/10/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 28/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 07/10/2026 — 1º e 2º tempos</t>
+          <t>Sexta, 02/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 19/10/2026 — 5º e 6º tempos</t>
+          <t>Terça, 06/10/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -2306,57 +2306,57 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 26/10/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 19/10/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 7º tempo</t>
+          <t>Segunda, 26/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 05/11/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 28/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -2366,37 +2366,37 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 09/11/2026 — 1º e 2º tempos</t>
+          <t>Quarta, 04/11/2026 — 1º tempo</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 11/11/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 12/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
@@ -2459,17 +2459,17 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 17/08/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 17/08/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
@@ -2479,17 +2479,17 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Terça, 18/08/2026 — 3º e 4º tempos</t>
+          <t>Terça, 18/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -2499,17 +2499,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 21/08/2026 — 3º e 4º tempos</t>
+          <t>Quarta, 19/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -2519,57 +2519,57 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>S3-11</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Terça, 25/08 e Quarta, 26/08/2026 — 2º ao 7º tempos</t>
+          <t>Segunda, 24/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>S3-11</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 27/08/2026 — 4º e 5º tempos</t>
+          <t>Terça, 25/08 e Quarta, 26/08/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 31/08/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 27/08/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -2579,37 +2579,37 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Terça, 01/09/2026 — 1º e 2º tempos</t>
+          <t>Segunda, 31/08/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 1º e 2º tempos</t>
+          <t>Quarta, 02/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -2619,17 +2619,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 03/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -2639,37 +2639,37 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 10/09/2026 — 2º ao 4º tempos</t>
+          <t>Terça, 08/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 11/09/2026 — 3º e 4º tempos</t>
+          <t>Quinta, 10/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 14/09/2026 — 1º e 2º tempos</t>
+          <t>Terça, 15/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -2739,57 +2739,57 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 28/09/2026 — 1º e 2º tempos</t>
+          <t>Segunda, 28/09/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Terça, 29/09/2026 — 1º e 2º tempos</t>
+          <t>Quarta, 07/10/2026 — 11º tempo</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 08/10/2026 — 1º e 2º tempos</t>
+          <t>Segunda, 19/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -2799,77 +2799,77 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 19/10/2026 — 2º ao 4º tempos</t>
+          <t>Terça, 20/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>S4-11</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 9º tempo</t>
+          <t>Segunda, 26/10 e Terça, 27/10/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>S4-11</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 26/10 e Terça, 27/10/2026 — 2º ao 7º tempos</t>
+          <t>Quarta, 04/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 3º e 4º tempos</t>
+          <t>Quinta, 05/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 09/11/2026 — 5º e 6º tempos</t>
+          <t>Terça, 10/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
@@ -2899,17 +2899,17 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 13/11/2026 — 3º e 4º tempos</t>
+          <t>Quinta, 12/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
@@ -2919,17 +2919,17 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 19/11/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 16/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
@@ -2992,17 +2992,17 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 17/08/2026 — 3º e 4º tempos</t>
+          <t>Segunda, 17/08/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
@@ -3012,17 +3012,17 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 19/08/2026 — 1º e 2º tempos</t>
+          <t>Terça, 18/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -3032,17 +3032,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 20/08/2026 — 3º e 4º tempos</t>
+          <t>Quarta, 19/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -3052,17 +3052,17 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 24/08/2026 — 5º e 6º tempos</t>
+          <t>Segunda, 24/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -3092,17 +3092,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 27/08/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 27/08/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -3112,37 +3112,37 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 31/08/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 31/08/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Terça, 01/09/2026 — 1º e 2º tempos</t>
+          <t>Quarta, 02/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -3152,17 +3152,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 02/09/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 03/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -3172,17 +3172,17 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 3º e 4º tempos</t>
+          <t>Terça, 08/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -3192,37 +3192,37 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 10/09/2026 — 4º ao 6º tempos</t>
+          <t>Quinta, 10/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 14/09/2026 — 5º e 6º tempos</t>
+          <t>Terça, 15/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -3232,17 +3232,17 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 16/09/2026 — 11º tempo</t>
+          <t>Sexta, 18/09/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -3252,17 +3252,17 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 21/09/2026 — 1º e 2º tempos</t>
+          <t>Segunda, 21/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -3272,21 +3272,21 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 23/09/2026 — 1º e 2º tempos</t>
+          <t>Segunda, 28/09/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 28/09/2026 — 3º e 4º tempos</t>
+          <t>Segunda, 05/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -3312,17 +3312,17 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 02/10/2026 — 4º tempo</t>
+          <t>Quarta, 07/10/2026 — 11º tempo</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -3332,17 +3332,17 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 05/10/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 19/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -3352,17 +3352,17 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 1º e 2º tempos</t>
+          <t>Terça, 20/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -3392,37 +3392,37 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 05/11/2026 — 4º ao 6º tempos</t>
+          <t>Quarta, 04/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 09/11/2026 — 2º e 3º tempos</t>
+          <t>Terça, 10/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 12/11/2026 — 3º e 4º tempos</t>
+          <t>Quinta, 12/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Terça, 17/11/2026 — 1º e 2º tempos</t>
+          <t>Segunda, 16/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
@@ -3525,17 +3525,17 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 17/08/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 17/08/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
@@ -3545,17 +3545,17 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Terça, 18/08/2026 — 5º e 6º tempos</t>
+          <t>Quinta, 20/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -3565,21 +3565,21 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 20/08/2026 — 3º ao 5º tempos</t>
+          <t>Sexta, 21/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 24/08/2026 — 3º e 4º tempos</t>
+          <t>Segunda, 24/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -3605,17 +3605,17 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Terça, 25/08/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 28/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -3625,17 +3625,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 26/08/2026 — 5º e 6º tempos</t>
+          <t>Terça, 01/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -3645,17 +3645,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 31/08/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 03/09/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -3665,17 +3665,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 04/09/2026 — 3º e 4º tempos</t>
+          <t>Sexta, 04/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -3685,12 +3685,12 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -3705,77 +3705,77 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 11/09/2026 — 1º e 2º tempos</t>
+          <t>Sexta, 11/09/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>S4-12</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 14/09/2026 — 3º e 4º tempos</t>
+          <t>Quarta, 16/09 e Quinta, 17/09/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>S4-12</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 16/09 e Quinta, 17/09/2026 — 2º ao 7º tempos</t>
+          <t>Sexta, 18/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 21/09/2026 — 1º e 2º tempos</t>
+          <t>Terça, 22/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -3785,37 +3785,37 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 23/09/2026 — 2º tempo</t>
+          <t>Quinta, 24/09/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Terça, 29/09/2026 — 1º e 2º tempos</t>
+          <t>Segunda, 28/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -3835,7 +3835,7 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 05/10/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 02/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -3845,17 +3845,17 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 09/10/2026 — 3º e 4º tempos</t>
+          <t>Segunda, 05/10/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -3865,77 +3865,77 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 5º e 6º tempos</t>
+          <t>Quarta, 07/10/2026 — 4º tempo</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 10º tempo</t>
+          <t>Terça, 20/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 3º ao 5º tempos</t>
+          <t>Sexta, 23/10/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Terça, 03/11/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 29/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -3945,41 +3945,41 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 09/11/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 06/11/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Terça, 10/11/2026 — 5º e 6º tempos</t>
+          <t>Quarta, 11/11/2026 — 6º tempo</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4038,17 +4038,17 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 17/08/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 17/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
@@ -4058,17 +4058,17 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 19/08/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 20/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -4078,17 +4078,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 24/08/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 21/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -4098,17 +4098,17 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Terça, 25/08/2026 — 1º e 2º tempos</t>
+          <t>Segunda, 24/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -4118,17 +4118,17 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 28/08/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 28/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -4138,17 +4138,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 31/08/2026 — 3º e 4º tempos</t>
+          <t>Terça, 01/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -4158,17 +4158,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Terça, 01/09/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 03/09/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -4178,17 +4178,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 02/09/2026 — 1º e 2º tempos</t>
+          <t>Sexta, 04/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -4198,17 +4198,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 5º e 6º tempos</t>
+          <t>Terça, 08/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 11/09/2026 — 2º ao 4º tempos</t>
+          <t>Sexta, 11/09/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -4258,17 +4258,17 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Terça, 22/09/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 18/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -4278,17 +4278,17 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 23/09/2026 — 1º e 2º tempos</t>
+          <t>Terça, 22/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -4298,7 +4298,7 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 28/09/2026 — 3º e 4º tempos</t>
+          <t>Quinta, 24/09/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -4318,17 +4318,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Terça, 29/09/2026 — 1º e 2º tempos</t>
+          <t>Segunda, 28/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -4338,17 +4338,17 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 05/10/2026 — 1º e 2º tempos</t>
+          <t>Sexta, 02/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -4358,17 +4358,17 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 07/10/2026 — 6º tempo</t>
+          <t>Quarta, 07/10/2026 — 4º tempo</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -4378,17 +4378,17 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 5º e 6º tempos</t>
+          <t>Terça, 20/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -4398,37 +4398,37 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 23/10/2026 — 2º ao 4º tempos</t>
+          <t>Sexta, 23/10/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 26/10/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 29/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -4438,37 +4438,37 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 06/11/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 06/11/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 09/11/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 09/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
@@ -4478,17 +4478,17 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 11/11/2026 — 4º tempo</t>
+          <t>Quarta, 11/11/2026 — 6º tempo</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_1.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_1.xlsx
@@ -1533,17 +1533,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 31/08/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 27/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -1553,17 +1553,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 31/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -1573,17 +1573,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 04/09/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 03/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -1653,37 +1653,37 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 14/09/2026 — 1º e 2º tempos</t>
+          <t>Segunda, 14/09/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 16/09/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -1693,77 +1693,77 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 23/09/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 25/09/2026 — 5º tempo</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 25/09/2026 — 5º tempo</t>
+          <t>Segunda, 28/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 28/09/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 30/09/2026 — 1º tempo</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 02/10/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 08/10/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -1773,17 +1773,17 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Terça, 06/10/2026 — 10º e 11º tempos</t>
+          <t>Quinta, 22/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -1793,37 +1793,37 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 19/10/2026 — 1º ao 3º tempos</t>
+          <t>Segunda, 26/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 26/10/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -1833,17 +1833,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 04/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -1853,37 +1853,37 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 1º tempo</t>
+          <t>Quinta, 05/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 12/11/2026 — 2º e 3º tempos</t>
+          <t>Terça, 10/11/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
@@ -2046,17 +2046,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Terça, 01/09/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 27/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -2066,17 +2066,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 2º e 3º tempos</t>
+          <t>Terça, 01/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -2086,17 +2086,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 04/09/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 03/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -2166,37 +2166,37 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 14/09/2026 — 1º e 2º tempos</t>
+          <t>Segunda, 14/09/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 16/09/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -2206,77 +2206,77 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 23/09/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 25/09/2026 — 5º tempo</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 25/09/2026 — 5º tempo</t>
+          <t>Segunda, 28/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 28/09/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 30/09/2026 — 1º tempo</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 02/10/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 08/10/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -2286,17 +2286,17 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Terça, 06/10/2026 — 10º e 11º tempos</t>
+          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -2306,32 +2306,32 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 19/10/2026 — 1º ao 3º tempos</t>
+          <t>Quinta, 22/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -2346,17 +2346,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 04/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -2366,37 +2366,37 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 1º tempo</t>
+          <t>Quinta, 05/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 12/11/2026 — 2º e 3º tempos</t>
+          <t>Terça, 10/11/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
@@ -3525,17 +3525,17 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 17/08/2026 — 1º e 2º tempos</t>
+          <t>Terça, 18/08/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
@@ -3545,17 +3545,17 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 20/08/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 21/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -3565,17 +3565,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 21/08/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 24/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -3585,17 +3585,17 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 24/08/2026 — 4º e 5º tempos</t>
+          <t>Terça, 25/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -3605,17 +3605,17 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 28/08/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 28/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -3665,17 +3665,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 04/09/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 04/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -3685,17 +3685,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 10/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -3745,17 +3745,17 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 18/09/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 24/09/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -3765,17 +3765,17 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Terça, 22/09/2026 — 1º e 2º tempos</t>
+          <t>Sexta, 25/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -3785,7 +3785,7 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 24/09/2026 — 9º e 10º tempos</t>
+          <t>Segunda, 28/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -3805,17 +3805,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 28/09/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 05/10/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -3825,37 +3825,37 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 02/10/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 09/10/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 05/10/2026 — 1º e 2º tempos</t>
+          <t>Terça, 20/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 07/10/2026 — 4º tempo</t>
+          <t>Quarta, 21/10/2026 — 4º tempo</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -3885,17 +3885,17 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 2º e 3º tempos</t>
+          <t>Terça, 27/10/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -3905,17 +3905,17 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 23/10/2026 — 1º e 2º tempos</t>
+          <t>Sexta, 30/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -3925,17 +3925,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 05/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -3945,21 +3945,21 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 06/11/2026 — 1º ao 3º tempos</t>
+          <t>Sexta, 06/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -4068,7 +4068,7 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 20/08/2026 — 4º e 5º tempos</t>
+          <t>Terça, 18/08/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -4118,17 +4118,17 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 28/08/2026 — 4º e 5º tempos</t>
+          <t>Terça, 25/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -4138,17 +4138,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Terça, 01/09/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 28/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -4158,17 +4158,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 9º e 10º tempos</t>
+          <t>Terça, 01/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -4178,17 +4178,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 04/09/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 03/09/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -4198,17 +4198,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 1º e 2º tempos</t>
+          <t>Sexta, 04/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -4258,17 +4258,17 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 18/09/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 24/09/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -4278,17 +4278,17 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Terça, 22/09/2026 — 1º e 2º tempos</t>
+          <t>Sexta, 25/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -4298,7 +4298,7 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 24/09/2026 — 9º e 10º tempos</t>
+          <t>Segunda, 28/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -4318,37 +4318,37 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 28/09/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 09/10/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 02/10/2026 — 2º e 3º tempos</t>
+          <t>Terça, 20/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 07/10/2026 — 4º tempo</t>
+          <t>Quarta, 21/10/2026 — 4º tempo</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -4378,17 +4378,17 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 2º e 3º tempos</t>
+          <t>Terça, 27/10/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -4398,17 +4398,17 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 23/10/2026 — 1º e 2º tempos</t>
+          <t>Sexta, 30/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -4418,17 +4418,17 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 05/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -4438,21 +4438,21 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 06/11/2026 — 1º ao 3º tempos</t>
+          <t>Sexta, 06/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_1.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_1.xlsx
@@ -537,7 +537,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Terça, 18/08/2026 — 4º e 5º tempos</t>
+          <t>Terça, 25/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
@@ -557,7 +557,7 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 21/08/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 28/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -577,7 +577,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 26/08/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 02/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -597,7 +597,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 27/08/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 03/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -617,7 +617,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 02/09/2026 — 6º e 7º tempos</t>
+          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -637,7 +637,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 10/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 16/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -677,7 +677,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 11/09/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 18/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -697,7 +697,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 16/09/2026 — 6º e 7º tempos</t>
+          <t>Quarta, 23/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -707,37 +707,37 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 23/09/2026 — 2º tempo</t>
+          <t>Quinta, 24/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 24/09/2026 — 1º e 2º tempos</t>
+          <t>Quarta, 30/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
@@ -767,37 +767,37 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Terça, 06/10/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 05/10/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
+          <t>Terça, 20/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -807,41 +807,41 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 23/10/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 28/10/2026 — 3º tempo</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 26/10/2026 — 2º tempo</t>
+          <t>Sexta, 30/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -887,41 +887,41 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 16/11/2026 — 1º tempo</t>
+          <t>Quinta, 12/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 19/11/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 18/11/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -990,7 +990,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Terça, 18/08/2026 — 4º e 5º tempos</t>
+          <t>Terça, 25/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 21/08/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 28/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 26/08/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 02/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 27/08/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 03/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 02/09/2026 — 6º e 7º tempos</t>
+          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 10/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 16/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 11/09/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 18/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 16/09/2026 — 6º e 7º tempos</t>
+          <t>Quarta, 23/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -1160,37 +1160,37 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 23/09/2026 — 2º tempo</t>
+          <t>Quinta, 24/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 24/09/2026 — 1º e 2º tempos</t>
+          <t>Quarta, 30/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
@@ -1220,37 +1220,37 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Terça, 06/10/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 05/10/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
+          <t>Terça, 20/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -1260,41 +1260,41 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 23/10/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 28/10/2026 — 3º tempo</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 26/10/2026 — 2º tempo</t>
+          <t>Sexta, 30/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1340,41 +1340,41 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 16/11/2026 — 1º tempo</t>
+          <t>Quinta, 12/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 19/11/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 18/11/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 17/08/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 24/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 19/08/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 26/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -1473,37 +1473,37 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 20/08/2026 — 1º ao 3º tempos</t>
+          <t>Quinta, 27/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 24/08/2026 — 1º e 2º tempos</t>
+          <t>Segunda, 31/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -1513,17 +1513,17 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Terça, 25/08/2026 — 6º e 7º tempos</t>
+          <t>Quinta, 03/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -1533,17 +1533,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 27/08/2026 — 4º e 5º tempos</t>
+          <t>Terça, 08/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -1553,17 +1553,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 31/08/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 09/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -1573,17 +1573,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 10/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -1593,21 +1593,21 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 14/09/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 10/09/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 17/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 11/09/2026 — 2º ao 7º tempos</t>
+          <t>Sexta, 18/09/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
@@ -1653,21 +1653,21 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 14/09/2026 — 1º ao 3º tempos</t>
+          <t>Segunda, 21/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 24/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -1693,37 +1693,37 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 25/09/2026 — 5º tempo</t>
+          <t>Segunda, 28/09/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 28/09/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 01/10/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -1733,37 +1733,37 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 30/09/2026 — 1º tempo</t>
+          <t>Terça, 06/10/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 08/10/2026 — 1º e 2º tempos</t>
+          <t>Quarta, 21/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -1773,37 +1773,37 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 22/10/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 28/10/2026 — 1º tempo</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 26/10/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -1813,17 +1813,17 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 05/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -1833,37 +1833,37 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 06/11/2026 — 5º tempo</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 05/11/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 11/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
@@ -1873,17 +1873,17 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Terça, 10/11/2026 — 6º e 7º tempos</t>
+          <t>Quinta, 12/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 17/08/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 24/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 19/08/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 26/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -1986,37 +1986,37 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 20/08/2026 — 1º ao 3º tempos</t>
+          <t>Quinta, 27/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 24/08/2026 — 1º e 2º tempos</t>
+          <t>Terça, 01/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -2026,17 +2026,17 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Terça, 25/08/2026 — 6º e 7º tempos</t>
+          <t>Quinta, 03/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -2046,17 +2046,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 27/08/2026 — 4º e 5º tempos</t>
+          <t>Terça, 08/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -2066,17 +2066,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Terça, 01/09/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 09/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -2086,17 +2086,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 10/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -2106,21 +2106,21 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 14/09/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 10/09/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 17/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 11/09/2026 — 2º ao 7º tempos</t>
+          <t>Sexta, 18/09/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
@@ -2166,21 +2166,21 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 14/09/2026 — 1º ao 3º tempos</t>
+          <t>Segunda, 21/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 24/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -2206,37 +2206,37 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 25/09/2026 — 5º tempo</t>
+          <t>Segunda, 28/09/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 28/09/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 01/10/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -2246,37 +2246,37 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 30/09/2026 — 1º tempo</t>
+          <t>Terça, 06/10/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 08/10/2026 — 1º e 2º tempos</t>
+          <t>Quarta, 07/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -2286,17 +2286,17 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 21/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -2306,37 +2306,37 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 22/10/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 28/10/2026 — 1º tempo</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 26/10/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 05/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -2346,37 +2346,37 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 06/11/2026 — 5º tempo</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 05/11/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 11/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
@@ -2386,17 +2386,17 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Terça, 10/11/2026 — 6º e 7º tempos</t>
+          <t>Quinta, 12/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
@@ -2459,17 +2459,17 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 17/08/2026 — 1º e 2º tempos</t>
+          <t>Segunda, 24/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
@@ -2479,37 +2479,37 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>S3-11</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Terça, 18/08/2026 — 2º e 3º tempos</t>
+          <t>Terça, 25/08 e Quarta, 26/08/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 19/08/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 27/08/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -2519,17 +2519,17 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 24/08/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 31/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -2539,37 +2539,37 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>S3-11</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Terça, 25/08 e Quarta, 26/08/2026 — 2º ao 7º tempos</t>
+          <t>Terça, 01/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 27/08/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 03/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -2579,37 +2579,37 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 31/08/2026 — 1º ao 3º tempos</t>
+          <t>Terça, 08/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 02/09/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 10/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -2619,37 +2619,37 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 14/09/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 4º e 5º tempos</t>
+          <t>Terça, 15/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -2659,17 +2659,17 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 10/09/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 16/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
@@ -2679,57 +2679,57 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Terça, 15/09/2026 — 1º e 2º tempos</t>
+          <t>Sexta, 25/09/2026 — 4º tempo</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 18/09/2026 — 2º tempo</t>
+          <t>Segunda, 28/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 21/09/2026 — 2º e 3º tempos</t>
+          <t>Terça, 29/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 28/09/2026 — 1º ao 3º tempos</t>
+          <t>Segunda, 05/10/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -2759,37 +2759,37 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 07/10/2026 — 11º tempo</t>
+          <t>Terça, 20/10/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 19/10/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -2799,57 +2799,57 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>S4-11</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 26/10 e Terça, 27/10/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>S4-11</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 26/10 e Terça, 27/10/2026 — 2º ao 7º tempos</t>
+          <t>Quinta, 29/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 4º e 5º tempos</t>
+          <t>Terça, 03/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -2859,17 +2859,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 05/11/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 09/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -2879,17 +2879,17 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Terça, 10/11/2026 — 4º e 5º tempos</t>
+          <t>Terça, 10/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
@@ -2899,37 +2899,37 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 12/11/2026 — 1º e 2º tempos</t>
+          <t>Quarta, 18/11/2026 — 11º tempo</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 16/11/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 19/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
@@ -2992,17 +2992,17 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 17/08/2026 — 1º e 2º tempos</t>
+          <t>Segunda, 24/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
@@ -3012,37 +3012,37 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>S3-11</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Terça, 18/08/2026 — 2º e 3º tempos</t>
+          <t>Terça, 25/08 e Quarta, 26/08/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 19/08/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 27/08/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -3052,17 +3052,17 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 24/08/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 31/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -3072,37 +3072,37 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>S3-11</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Terça, 25/08 e Quarta, 26/08/2026 — 2º ao 7º tempos</t>
+          <t>Terça, 01/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 27/08/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 03/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -3112,37 +3112,37 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 31/08/2026 — 1º ao 3º tempos</t>
+          <t>Terça, 08/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 02/09/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 10/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -3152,37 +3152,37 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 1º e 2º tempos</t>
+          <t>Segunda, 14/09/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 4º e 5º tempos</t>
+          <t>Terça, 15/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -3192,17 +3192,17 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 10/09/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 16/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
@@ -3212,17 +3212,17 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Terça, 15/09/2026 — 1º e 2º tempos</t>
+          <t>Segunda, 21/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 18/09/2026 — 2º tempo</t>
+          <t>Sexta, 25/09/2026 — 4º tempo</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -3252,17 +3252,17 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 21/09/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 28/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -3272,77 +3272,77 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 28/09/2026 — 1º ao 3º tempos</t>
+          <t>Terça, 29/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 05/10/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 05/10/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 07/10/2026 — 11º tempo</t>
+          <t>Terça, 20/10/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 19/10/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -3352,57 +3352,57 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>S4-11</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 26/10 e Terça, 27/10/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>S4-11</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 26/10 e Terça, 27/10/2026 — 2º ao 7º tempos</t>
+          <t>Terça, 03/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 09/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -3412,17 +3412,17 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Terça, 10/11/2026 — 4º e 5º tempos</t>
+          <t>Terça, 10/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
@@ -3432,37 +3432,37 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 12/11/2026 — 1º e 2º tempos</t>
+          <t>Quarta, 18/11/2026 — 11º tempo</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 16/11/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 19/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
@@ -3525,17 +3525,17 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Terça, 18/08/2026 — 1º e 2º tempos</t>
+          <t>Segunda, 24/08/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
@@ -3545,17 +3545,17 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 21/08/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 27/08/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -3565,37 +3565,37 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 24/08/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 28/08/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Terça, 25/08/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 31/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -3605,17 +3605,17 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 28/08/2026 — 2º e 3º tempos</t>
+          <t>Terça, 01/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -3625,17 +3625,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Terça, 01/09/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 04/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -3645,17 +3645,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 9º e 10º tempos</t>
+          <t>Terça, 08/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -3665,17 +3665,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 04/09/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 11/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -3685,17 +3685,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 10/09/2026 — 4º e 5º tempos</t>
+          <t>Terça, 15/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -3705,57 +3705,57 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>S4-12</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 11/09/2026 — 1º ao 3º tempos</t>
+          <t>Quarta, 16/09 e Quinta, 17/09/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>S4-12</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 16/09 e Quinta, 17/09/2026 — 2º ao 7º tempos</t>
+          <t>Sexta, 18/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 24/09/2026 — 9º e 10º tempos</t>
+          <t>Terça, 22/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -3765,17 +3765,17 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 25/09/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 24/09/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -3785,37 +3785,37 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 28/09/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 30/09/2026 — 4º tempo</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 05/10/2026 — 1º e 2º tempos</t>
+          <t>Sexta, 02/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -3825,37 +3825,37 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 09/10/2026 — 1º ao 3º tempos</t>
+          <t>Terça, 06/10/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 09/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -3865,57 +3865,57 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 4º tempo</t>
+          <t>Terça, 20/10/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Terça, 27/10/2026 — 1º e 2º tempos</t>
+          <t>Sexta, 23/10/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 30/10/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 26/10/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -3925,17 +3925,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 05/11/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 30/10/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -3945,41 +3945,41 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 06/11/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 04/11/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 11/11/2026 — 6º tempo</t>
+          <t>Segunda, 09/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 17/08/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 24/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
@@ -4058,17 +4058,17 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Terça, 18/08/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 27/08/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -4078,21 +4078,21 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 21/08/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 28/08/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 24/08/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 31/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Terça, 25/08/2026 — 2º e 3º tempos</t>
+          <t>Terça, 01/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 28/08/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 04/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -4158,17 +4158,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Terça, 01/09/2026 — 2º e 3º tempos</t>
+          <t>Terça, 08/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -4178,17 +4178,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 9º e 10º tempos</t>
+          <t>Sexta, 11/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -4198,17 +4198,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 04/09/2026 — 4º e 5º tempos</t>
+          <t>Terça, 15/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -4218,57 +4218,57 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>S4-12</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 11/09/2026 — 1º ao 3º tempos</t>
+          <t>Quarta, 16/09 e Quinta, 17/09/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>S4-12</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 16/09 e Quinta, 17/09/2026 — 2º ao 7º tempos</t>
+          <t>Sexta, 18/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 24/09/2026 — 9º e 10º tempos</t>
+          <t>Terça, 22/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -4278,17 +4278,17 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 25/09/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 24/09/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -4298,57 +4298,57 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 28/09/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 30/09/2026 — 4º tempo</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 09/10/2026 — 1º ao 3º tempos</t>
+          <t>Sexta, 02/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 2º e 3º tempos</t>
+          <t>Terça, 06/10/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -4358,37 +4358,37 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 4º tempo</t>
+          <t>Sexta, 09/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Terça, 27/10/2026 — 1º e 2º tempos</t>
+          <t>Terça, 20/10/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -4398,37 +4398,37 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 30/10/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 23/10/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 05/11/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 26/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 06/11/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 30/10/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -4458,41 +4458,41 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 09/11/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 04/11/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 11/11/2026 — 6º tempo</t>
+          <t>Segunda, 09/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_1.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_1.xlsx
@@ -1453,17 +1453,17 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 26/08/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 27/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -1473,17 +1473,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 27/08/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 28/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -1513,17 +1513,17 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 02/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -1533,17 +1533,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 6º e 7º tempos</t>
+          <t>Quinta, 03/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -1553,17 +1553,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 2º e 3º tempos</t>
+          <t>Terça, 08/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -1573,57 +1573,57 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 10/09/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 10/09/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 14/09/2026 — 1º ao 3º tempos</t>
+          <t>Segunda, 14/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 17/09/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 17/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -1633,57 +1633,57 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>AG10</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 18/09/2026 — 2º ao 7º tempos</t>
+          <t>Segunda, 21/09/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>AG10</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 21/09/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 25/09/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 24/09/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 28/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -1693,21 +1693,21 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 28/09/2026 — 1º ao 3º tempos</t>
+          <t>Quinta, 01/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 01/10/2026 — 1º e 2º tempos</t>
+          <t>Segunda, 05/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Terça, 06/10/2026 — 10º e 11º tempos</t>
+          <t>Terça, 20/10/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -1753,17 +1753,17 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 22/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -1773,37 +1773,37 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 1º tempo</t>
+          <t>Quarta, 28/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 29/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -1813,21 +1813,21 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 05/11/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 04/11/2026 — 1º tempo</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1853,17 +1853,17 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 11/11/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 09/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
@@ -1873,17 +1873,17 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 12/11/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 11/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
@@ -1966,17 +1966,17 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 26/08/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 27/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -1986,17 +1986,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 27/08/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 28/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -2026,17 +2026,17 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 02/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -2046,17 +2046,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 6º e 7º tempos</t>
+          <t>Quinta, 03/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -2066,17 +2066,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 2º e 3º tempos</t>
+          <t>Terça, 08/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -2086,57 +2086,57 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 10/09/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 10/09/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 14/09/2026 — 1º ao 3º tempos</t>
+          <t>Segunda, 14/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 17/09/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 17/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -2146,57 +2146,57 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>AG10</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 18/09/2026 — 2º ao 7º tempos</t>
+          <t>Segunda, 21/09/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>AG10</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 21/09/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 25/09/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 24/09/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 28/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -2206,21 +2206,21 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 28/09/2026 — 1º ao 3º tempos</t>
+          <t>Quinta, 01/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 01/10/2026 — 1º e 2º tempos</t>
+          <t>Segunda, 05/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -2246,17 +2246,17 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Terça, 06/10/2026 — 10º e 11º tempos</t>
+          <t>Quarta, 07/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -2266,17 +2266,17 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 07/10/2026 — 4º e 5º tempos</t>
+          <t>Terça, 20/10/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 28/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -2306,41 +2306,41 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 1º tempo</t>
+          <t>Quinta, 29/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 05/11/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 04/11/2026 — 1º tempo</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -2366,17 +2366,17 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 11/11/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 09/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
@@ -2386,17 +2386,17 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 12/11/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 11/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
